--- a/salidas/empresas/CB.xlsx
+++ b/salidas/empresas/CB.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>36.18127822875977</v>
+        <v>36.1812858581543</v>
       </c>
       <c r="C2" t="n">
         <v>54.75</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>36.82889175415039</v>
+        <v>36.82888412475586</v>
       </c>
       <c r="C3" t="n">
         <v>55.72999954223633</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>34.52082061767578</v>
+        <v>34.52083206176758</v>
       </c>
       <c r="C4" t="n">
         <v>52.0099983215332</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>36.86380004882812</v>
+        <v>36.86380386352539</v>
       </c>
       <c r="C5" t="n">
         <v>55.54000091552734</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>34.36153030395508</v>
+        <v>34.36152648925781</v>
       </c>
       <c r="C6" t="n">
         <v>51.77000045776367</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>33.75128936767578</v>
+        <v>33.75129699707031</v>
       </c>
       <c r="C7" t="n">
         <v>50.59000015258789</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>34.37841415405273</v>
+        <v>34.37841796875</v>
       </c>
       <c r="C8" t="n">
         <v>51.52999877929688</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>35.93289566040039</v>
+        <v>35.9328727722168</v>
       </c>
       <c r="C9" t="n">
         <v>53.86000061035156</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>36.67716217041016</v>
+        <v>36.67715835571289</v>
       </c>
       <c r="C10" t="n">
         <v>54.72999954223633</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>38.36594009399414</v>
+        <v>38.36593246459961</v>
       </c>
       <c r="C11" t="n">
         <v>57.25</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>38.09117126464844</v>
+        <v>38.09116744995117</v>
       </c>
       <c r="C12" t="n">
         <v>56.84000015258789</v>
@@ -691,7 +703,7 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>38.88091659545898</v>
+        <v>38.88089752197266</v>
       </c>
       <c r="C14" t="n">
         <v>57.77999877929688</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>37.77734375</v>
+        <v>37.7773323059082</v>
       </c>
       <c r="C15" t="n">
         <v>56.13999938964844</v>
@@ -748,7 +760,7 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>40.18602752685547</v>
+        <v>40.18603134155273</v>
       </c>
       <c r="C17" t="n">
         <v>59.45999908447266</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>41.61206817626953</v>
+        <v>41.61207580566406</v>
       </c>
       <c r="C18" t="n">
         <v>61.56999969482422</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>42.43849182128906</v>
+        <v>42.43849563598633</v>
       </c>
       <c r="C19" t="n">
         <v>62.52000045776367</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>39.18026351928711</v>
+        <v>39.18025970458984</v>
       </c>
       <c r="C20" t="n">
         <v>57.72000122070312</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>39.20740509033203</v>
+        <v>39.20742416381836</v>
       </c>
       <c r="C21" t="n">
         <v>57.7599983215332</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>41.30470275878906</v>
+        <v>41.30469131469727</v>
       </c>
       <c r="C22" t="n">
         <v>60.56999969482422</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>41.33197784423828</v>
+        <v>41.33197402954102</v>
       </c>
       <c r="C23" t="n">
         <v>60.61000061035156</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>40.80007934570312</v>
+        <v>40.80006790161133</v>
       </c>
       <c r="C24" t="n">
         <v>59.83000183105469</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>42.31157302856445</v>
+        <v>42.31157684326172</v>
       </c>
       <c r="C25" t="n">
         <v>61.77999877929688</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>39.88713455200195</v>
+        <v>39.88713073730469</v>
       </c>
       <c r="C26" t="n">
         <v>58.2400016784668</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>38.51737594604492</v>
+        <v>38.51736831665039</v>
       </c>
       <c r="C27" t="n">
         <v>56.2400016784668</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>37.89440536499023</v>
+        <v>37.89439392089844</v>
       </c>
       <c r="C28" t="n">
         <v>55.06000137329102</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>41.493896484375</v>
+        <v>41.49387741088867</v>
       </c>
       <c r="C29" t="n">
         <v>60.29000091552734</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>41.34249114990234</v>
+        <v>41.34247970581055</v>
       </c>
       <c r="C30" t="n">
         <v>60.06999969482422</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>38.10745239257812</v>
+        <v>38.1074333190918</v>
       </c>
       <c r="C31" t="n">
         <v>55.09000015258789</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>35.07075881958008</v>
+        <v>35.07075119018555</v>
       </c>
       <c r="C32" t="n">
         <v>50.70000076293945</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>36.3919677734375</v>
+        <v>36.39194869995117</v>
       </c>
       <c r="C33" t="n">
         <v>52.61000061035156</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>37.44337844848633</v>
+        <v>37.44338989257812</v>
       </c>
       <c r="C34" t="n">
         <v>54.13000106811523</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>39.90570068359375</v>
+        <v>39.90570449829102</v>
       </c>
       <c r="C35" t="n">
         <v>57.36000061035156</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>36.35062789916992</v>
+        <v>36.35064697265625</v>
       </c>
       <c r="C36" t="n">
         <v>52.25</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>36.81677627563477</v>
+        <v>36.81678009033203</v>
       </c>
       <c r="C37" t="n">
         <v>52.91999816894531</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>30.53106689453125</v>
+        <v>30.53106307983398</v>
       </c>
       <c r="C38" t="n">
         <v>43.65999984741211</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>25.53113746643066</v>
+        <v>25.53113555908203</v>
       </c>
       <c r="C39" t="n">
         <v>36.5099983215332</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>28.42901611328125</v>
+        <v>28.42902565002441</v>
       </c>
       <c r="C40" t="n">
         <v>40.40000152587891</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>32.5948600769043</v>
+        <v>32.59484100341797</v>
       </c>
       <c r="C41" t="n">
         <v>46.31999969482422</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>30.95525169372559</v>
+        <v>30.95525741577148</v>
       </c>
       <c r="C42" t="n">
         <v>43.9900016784668</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>31.1241397857666</v>
+        <v>31.12414169311523</v>
       </c>
       <c r="C43" t="n">
         <v>44.22999954223633</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>34.75038909912109</v>
+        <v>34.7503776550293</v>
       </c>
       <c r="C44" t="n">
         <v>49.06000137329102</v>
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>36.96035385131836</v>
+        <v>36.96034622192383</v>
       </c>
       <c r="C45" t="n">
         <v>52.18000030517578</v>
@@ -1324,7 +1336,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
@@ -1349,11 +1361,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>36.59368515014648</v>
+        <v>36.59368896484375</v>
       </c>
       <c r="C47" t="n">
         <v>51.36000061035156</v>
@@ -1374,11 +1386,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>34.70556259155273</v>
+        <v>34.7055778503418</v>
       </c>
       <c r="C48" t="n">
         <v>48.70999908447266</v>
@@ -1399,11 +1411,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>36.13235855102539</v>
+        <v>36.13236618041992</v>
       </c>
       <c r="C49" t="n">
         <v>50.40000152587891</v>
@@ -1424,11 +1436,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>35.32225036621094</v>
+        <v>35.3222541809082</v>
       </c>
       <c r="C50" t="n">
         <v>49.27000045776367</v>
@@ -1449,11 +1461,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>35.83844757080078</v>
+        <v>35.83843612670898</v>
       </c>
       <c r="C51" t="n">
         <v>49.9900016784668</v>
@@ -1474,11 +1486,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>37.71610641479492</v>
+        <v>37.71610260009766</v>
       </c>
       <c r="C52" t="n">
         <v>52.29999923706055</v>
@@ -1499,11 +1511,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>38.35793685913086</v>
+        <v>38.3579216003418</v>
       </c>
       <c r="C53" t="n">
         <v>53.18999862670898</v>
@@ -1524,7 +1536,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
@@ -1549,11 +1561,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>37.12478256225586</v>
+        <v>37.12474822998047</v>
       </c>
       <c r="C55" t="n">
         <v>51.47999954223633</v>
@@ -1574,11 +1586,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>38.51885986328125</v>
+        <v>38.51884460449219</v>
       </c>
       <c r="C56" t="n">
         <v>53.08000183105469</v>
@@ -1599,11 +1611,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>38.80187606811523</v>
+        <v>38.80186462402344</v>
       </c>
       <c r="C57" t="n">
         <v>53.47000122070312</v>
@@ -1624,11 +1636,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>42.51072311401367</v>
+        <v>42.51072692871094</v>
       </c>
       <c r="C58" t="n">
         <v>58.25</v>
@@ -1649,7 +1661,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
@@ -1668,11 +1680,11 @@
       <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>42.70776748657227</v>
+        <v>42.70774459838867</v>
       </c>
       <c r="C60" t="n">
         <v>58.52000045776367</v>
@@ -1693,11 +1705,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>45.67720794677734</v>
+        <v>45.67722320556641</v>
       </c>
       <c r="C61" t="n">
         <v>62.25</v>
@@ -1718,11 +1730,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>45.19293594360352</v>
+        <v>45.19293212890625</v>
       </c>
       <c r="C62" t="n">
         <v>61.59000015258789</v>
@@ -1743,11 +1755,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>46.41099548339844</v>
+        <v>46.41098785400391</v>
       </c>
       <c r="C63" t="n">
         <v>63.25</v>
@@ -1772,11 +1784,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>47.72097778320312</v>
+        <v>47.72098159790039</v>
       </c>
       <c r="C64" t="n">
         <v>64.69999694824219</v>
@@ -1801,11 +1813,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>49.60179901123047</v>
+        <v>49.60179138183594</v>
       </c>
       <c r="C65" t="n">
         <v>67.25</v>
@@ -1830,11 +1842,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>50.75976943969727</v>
+        <v>50.75978469848633</v>
       </c>
       <c r="C66" t="n">
         <v>68.81999969482422</v>
@@ -1859,11 +1871,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>48.81097412109375</v>
+        <v>48.81099700927734</v>
       </c>
       <c r="C67" t="n">
         <v>65.81999969482422</v>
@@ -1888,11 +1900,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>49.67122650146484</v>
+        <v>49.67121505737305</v>
       </c>
       <c r="C68" t="n">
         <v>66.98000335693359</v>
@@ -1917,11 +1929,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>47.89142227172852</v>
+        <v>47.89143371582031</v>
       </c>
       <c r="C69" t="n">
         <v>64.58000183105469</v>
@@ -1946,11 +1958,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>45.20025634765625</v>
+        <v>45.20026397705078</v>
       </c>
       <c r="C70" t="n">
         <v>60.59999847412109</v>
@@ -1975,11 +1987,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>53.81513214111328</v>
+        <v>53.81514358520508</v>
       </c>
       <c r="C71" t="n">
         <v>72.15000152587891</v>
@@ -2004,11 +2016,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>51.86095428466797</v>
+        <v>51.86094284057617</v>
       </c>
       <c r="C72" t="n">
         <v>69.52999877929688</v>
@@ -2033,11 +2045,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>52.30102157592773</v>
+        <v>52.30101776123047</v>
       </c>
       <c r="C73" t="n">
         <v>70.12000274658203</v>
@@ -2062,11 +2074,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>52.26231002807617</v>
+        <v>52.26233291625977</v>
       </c>
       <c r="C74" t="n">
         <v>69.59999847412109</v>
@@ -2091,11 +2103,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>53.84670257568359</v>
+        <v>53.84671783447266</v>
       </c>
       <c r="C75" t="n">
         <v>71.70999908447266</v>
@@ -2120,11 +2132,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>55.31957626342773</v>
+        <v>55.31958770751953</v>
       </c>
       <c r="C76" t="n">
         <v>73.19999694824219</v>
@@ -2149,11 +2161,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>57.4129638671875</v>
+        <v>57.41295623779297</v>
       </c>
       <c r="C77" t="n">
         <v>75.97000122070312</v>
@@ -2178,11 +2190,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>54.6620979309082</v>
+        <v>54.66209411621094</v>
       </c>
       <c r="C78" t="n">
         <v>72.33000183105469</v>
@@ -2207,11 +2219,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>56.02242660522461</v>
+        <v>56.02241516113281</v>
       </c>
       <c r="C79" t="n">
         <v>74.12999725341797</v>
@@ -2236,11 +2248,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>55.92562484741211</v>
+        <v>55.92564010620117</v>
       </c>
       <c r="C80" t="n">
         <v>73.5</v>
@@ -2265,7 +2277,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
@@ -2294,11 +2306,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>57.8990478515625</v>
+        <v>57.89902496337891</v>
       </c>
       <c r="C82" t="n">
         <v>75.59999847412109</v>
@@ -2323,7 +2335,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
@@ -2352,11 +2364,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>60.67911148071289</v>
+        <v>60.67911529541016</v>
       </c>
       <c r="C84" t="n">
         <v>79.23000335693359</v>
@@ -2381,11 +2393,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>61.4881706237793</v>
+        <v>61.48818969726562</v>
       </c>
       <c r="C85" t="n">
         <v>79.80000305175781</v>
@@ -2410,11 +2422,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>65.74916839599609</v>
+        <v>65.74919128417969</v>
       </c>
       <c r="C86" t="n">
         <v>85.33000183105469</v>
@@ -2439,11 +2451,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>65.79538726806641</v>
+        <v>65.79541778564453</v>
       </c>
       <c r="C87" t="n">
         <v>85.38999938964844</v>
@@ -2468,7 +2480,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
@@ -2497,11 +2509,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>69.06746673583984</v>
+        <v>69.06742858886719</v>
       </c>
       <c r="C89" t="n">
         <v>89.13999938964844</v>
@@ -2526,11 +2538,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>69.48582458496094</v>
+        <v>69.48584747314453</v>
       </c>
       <c r="C90" t="n">
         <v>89.68000030517578</v>
@@ -2555,11 +2567,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>69.33087158203125</v>
+        <v>69.33085632324219</v>
       </c>
       <c r="C91" t="n">
         <v>89.48000335693359</v>
@@ -2584,7 +2596,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
@@ -2613,7 +2625,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
@@ -2642,11 +2654,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>73.27458190917969</v>
+        <v>73.27457427978516</v>
       </c>
       <c r="C94" t="n">
         <v>93.55999755859375</v>
@@ -2671,11 +2683,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>74.74697875976562</v>
+        <v>74.74698638916016</v>
       </c>
       <c r="C95" t="n">
         <v>95.44000244140625</v>
@@ -2700,11 +2712,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>80.49554443359375</v>
+        <v>80.49553680419922</v>
       </c>
       <c r="C96" t="n">
         <v>102.7799987792969</v>
@@ -2729,11 +2741,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>81.08290100097656</v>
+        <v>81.08289337158203</v>
       </c>
       <c r="C97" t="n">
         <v>103.5299987792969</v>
@@ -2758,11 +2770,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>73.9425048828125</v>
+        <v>73.94251251220703</v>
       </c>
       <c r="C98" t="n">
         <v>93.80999755859375</v>
@@ -2787,11 +2799,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>77.14263916015625</v>
+        <v>77.14265441894531</v>
       </c>
       <c r="C99" t="n">
         <v>97.87000274658203</v>
@@ -2816,11 +2828,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>78.58001708984375</v>
+        <v>78.58003234863281</v>
       </c>
       <c r="C100" t="n">
         <v>99.05999755859375</v>
@@ -2845,11 +2857,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>81.16605377197266</v>
+        <v>81.16603088378906</v>
       </c>
       <c r="C101" t="n">
         <v>102.3199996948242</v>
@@ -2874,11 +2886,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>82.26863861083984</v>
+        <v>82.26866912841797</v>
       </c>
       <c r="C102" t="n">
         <v>103.7099990844727</v>
@@ -2903,7 +2915,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
@@ -2932,11 +2944,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>79.904052734375</v>
+        <v>79.90401458740234</v>
       </c>
       <c r="C104" t="n">
         <v>100.0999984741211</v>
@@ -2961,11 +2973,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>84.87704467773438</v>
+        <v>84.87709808349609</v>
       </c>
       <c r="C105" t="n">
         <v>106.3300018310547</v>
@@ -2990,11 +3002,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>84.23059844970703</v>
+        <v>84.23062133789062</v>
       </c>
       <c r="C106" t="n">
         <v>104.870002746582</v>
@@ -3019,7 +3031,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
@@ -3048,11 +3060,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>91.83681488037109</v>
+        <v>91.83679962158203</v>
       </c>
       <c r="C108" t="n">
         <v>114.3399963378906</v>
@@ -3077,11 +3089,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>92.8028564453125</v>
+        <v>92.80286407470703</v>
       </c>
       <c r="C109" t="n">
         <v>114.879997253418</v>
@@ -3106,11 +3118,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>87.21269226074219</v>
+        <v>87.21269989013672</v>
       </c>
       <c r="C110" t="n">
         <v>107.9599990844727</v>
@@ -3135,7 +3147,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
@@ -3164,11 +3176,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>90.59357452392578</v>
+        <v>90.59358978271484</v>
       </c>
       <c r="C112" t="n">
         <v>111.4899978637695</v>
@@ -3193,11 +3205,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>86.93701934814453</v>
+        <v>86.93702697753906</v>
       </c>
       <c r="C113" t="n">
         <v>106.9899978637695</v>
@@ -3222,11 +3234,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>86.52260589599609</v>
+        <v>86.52262115478516</v>
       </c>
       <c r="C114" t="n">
         <v>106.4800033569336</v>
@@ -3251,11 +3263,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>83.16456604003906</v>
+        <v>83.16455078125</v>
       </c>
       <c r="C115" t="n">
         <v>101.6800003051758</v>
@@ -3280,11 +3292,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>88.96348571777344</v>
+        <v>88.9635009765625</v>
       </c>
       <c r="C116" t="n">
         <v>108.7699966430664</v>
@@ -3309,11 +3321,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>83.55713653564453</v>
+        <v>83.55715942382812</v>
       </c>
       <c r="C117" t="n">
         <v>102.1600036621094</v>
@@ -3338,11 +3350,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>85.12284088134766</v>
+        <v>85.12281036376953</v>
       </c>
       <c r="C118" t="n">
         <v>103.4000015258789</v>
@@ -3367,11 +3379,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>93.47045135498047</v>
+        <v>93.47043609619141</v>
       </c>
       <c r="C119" t="n">
         <v>113.5400009155273</v>
@@ -3396,7 +3408,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
@@ -3425,11 +3437,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>96.74346160888672</v>
+        <v>96.74348449707031</v>
       </c>
       <c r="C121" t="n">
         <v>116.8499984741211</v>
@@ -3454,11 +3466,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>93.61387634277344</v>
+        <v>93.61392211914062</v>
       </c>
       <c r="C122" t="n">
         <v>113.0699996948242</v>
@@ -3483,11 +3495,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>95.65060424804688</v>
+        <v>95.65061187744141</v>
       </c>
       <c r="C123" t="n">
         <v>115.5299987792969</v>
@@ -3512,11 +3524,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>99.20523834228516</v>
+        <v>99.20525360107422</v>
       </c>
       <c r="C124" t="n">
         <v>119.1500015258789</v>
@@ -3541,11 +3553,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>98.13114929199219</v>
+        <v>98.13115692138672</v>
       </c>
       <c r="C125" t="n">
         <v>117.8600006103516</v>
@@ -3570,11 +3582,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>105.4164733886719</v>
+        <v>105.41650390625</v>
       </c>
       <c r="C126" t="n">
         <v>126.6100006103516</v>
@@ -3599,11 +3611,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>109.4500579833984</v>
+        <v>109.450065612793</v>
       </c>
       <c r="C127" t="n">
         <v>130.7100067138672</v>
@@ -3628,7 +3640,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
@@ -3657,11 +3669,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>106.2848739624023</v>
+        <v>106.2848815917969</v>
       </c>
       <c r="C129" t="n">
         <v>126.9300003051758</v>
@@ -3686,11 +3698,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>105.7957458496094</v>
+        <v>105.7957534790039</v>
       </c>
       <c r="C130" t="n">
         <v>125.6500015258789</v>
@@ -3715,11 +3727,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>106.9324417114258</v>
+        <v>106.9324340820312</v>
       </c>
       <c r="C131" t="n">
         <v>127</v>
@@ -3744,7 +3756,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
@@ -3773,11 +3785,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>111.8249435424805</v>
+        <v>111.8249588012695</v>
       </c>
       <c r="C133" t="n">
         <v>132.1199951171875</v>
@@ -3802,7 +3814,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
@@ -3831,11 +3843,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>116.9456024169922</v>
+        <v>116.9456405639648</v>
       </c>
       <c r="C135" t="n">
         <v>138.1699981689453</v>
@@ -3860,7 +3872,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
@@ -3889,11 +3901,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>116.7507171630859</v>
+        <v>116.7506866455078</v>
       </c>
       <c r="C137" t="n">
         <v>137.25</v>
@@ -3918,11 +3930,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>121.8035049438477</v>
+        <v>121.8034973144531</v>
       </c>
       <c r="C138" t="n">
         <v>143.1900024414062</v>
@@ -3947,11 +3959,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>124.2758255004883</v>
+        <v>124.2758407592773</v>
       </c>
       <c r="C139" t="n">
         <v>145.3800048828125</v>
@@ -3976,11 +3988,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>125.1990661621094</v>
+        <v>125.1990814208984</v>
       </c>
       <c r="C140" t="n">
         <v>146.4600067138672</v>
@@ -4005,7 +4017,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
@@ -4034,11 +4046,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>122.4693908691406</v>
+        <v>122.4694290161133</v>
       </c>
       <c r="C142" t="n">
         <v>142.5500030517578</v>
@@ -4063,11 +4075,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>129.574462890625</v>
+        <v>129.5744476318359</v>
       </c>
       <c r="C143" t="n">
         <v>150.8200073242188</v>
@@ -4092,11 +4104,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>130.6827087402344</v>
+        <v>130.6826782226562</v>
       </c>
       <c r="C144" t="n">
         <v>152.1100006103516</v>
@@ -4121,11 +4133,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>126.1578903198242</v>
+        <v>126.1578521728516</v>
       </c>
       <c r="C145" t="n">
         <v>146.1300048828125</v>
@@ -4150,7 +4162,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
@@ -4179,11 +4191,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>122.5232620239258</v>
+        <v>122.5233001708984</v>
       </c>
       <c r="C147" t="n">
         <v>141.9199981689453</v>
@@ -4208,7 +4220,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
@@ -4237,11 +4249,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>117.739013671875</v>
+        <v>117.7390365600586</v>
       </c>
       <c r="C149" t="n">
         <v>135.6699981689453</v>
@@ -4266,7 +4278,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
@@ -4295,11 +4307,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>110.8709945678711</v>
+        <v>110.8710098266602</v>
       </c>
       <c r="C151" t="n">
         <v>127.0199966430664</v>
@@ -4324,11 +4336,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>121.9563522338867</v>
+        <v>121.9563674926758</v>
       </c>
       <c r="C152" t="n">
         <v>139.7200012207031</v>
@@ -4353,11 +4365,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>118.0459365844727</v>
+        <v>118.0459442138672</v>
       </c>
       <c r="C153" t="n">
         <v>135.2400054931641</v>
@@ -4382,11 +4394,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>117.2602462768555</v>
+        <v>117.2602844238281</v>
       </c>
       <c r="C154" t="n">
         <v>133.6399993896484</v>
@@ -4411,11 +4423,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>109.6002578735352</v>
+        <v>109.6002655029297</v>
       </c>
       <c r="C155" t="n">
         <v>124.9100036621094</v>
@@ -4440,11 +4452,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>117.3479919433594</v>
+        <v>117.3479995727539</v>
       </c>
       <c r="C156" t="n">
         <v>133.7400054931641</v>
@@ -4469,7 +4481,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
@@ -4498,11 +4510,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>117.4193801879883</v>
+        <v>117.4193649291992</v>
       </c>
       <c r="C158" t="n">
         <v>133.0500030517578</v>
@@ -4527,7 +4539,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
@@ -4556,11 +4568,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>124.297004699707</v>
+        <v>124.2970352172852</v>
       </c>
       <c r="C160" t="n">
         <v>140.0800018310547</v>
@@ -4585,11 +4597,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>128.840087890625</v>
+        <v>128.8401184082031</v>
       </c>
       <c r="C161" t="n">
         <v>145.1999969482422</v>
@@ -4614,11 +4626,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>129.612060546875</v>
+        <v>129.6121215820312</v>
       </c>
       <c r="C162" t="n">
         <v>146.0700073242188</v>
@@ -4643,11 +4655,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>131.3538665771484</v>
+        <v>131.3538360595703</v>
       </c>
       <c r="C163" t="n">
         <v>147.2899932861328</v>
@@ -4672,7 +4684,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
@@ -4701,11 +4713,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>139.3711547851562</v>
+        <v>139.3711700439453</v>
       </c>
       <c r="C165" t="n">
         <v>156.2799987792969</v>
@@ -4730,7 +4742,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
@@ -4759,11 +4771,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>136.5710144042969</v>
+        <v>136.5710601806641</v>
       </c>
       <c r="C167" t="n">
         <v>152.4199981689453</v>
@@ -4788,7 +4800,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
@@ -4817,11 +4829,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>140.1540222167969</v>
+        <v>140.1539916992188</v>
       </c>
       <c r="C169" t="n">
         <v>155.6600036621094</v>
@@ -4846,11 +4858,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>136.8495483398438</v>
+        <v>136.8495941162109</v>
       </c>
       <c r="C170" t="n">
         <v>151.9900054931641</v>
@@ -4875,11 +4887,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>130.5829010009766</v>
+        <v>130.5828857421875</v>
       </c>
       <c r="C171" t="n">
         <v>145.0299987792969</v>
@@ -4904,11 +4916,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>101.3254547119141</v>
+        <v>101.3254470825195</v>
       </c>
       <c r="C172" t="n">
         <v>111.6900024414062</v>
@@ -4933,11 +4945,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>97.9869384765625</v>
+        <v>97.98694610595703</v>
       </c>
       <c r="C173" t="n">
         <v>108.0100021362305</v>
@@ -4962,7 +4974,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
@@ -4991,11 +5003,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>115.5649795532227</v>
+        <v>115.5649642944336</v>
       </c>
       <c r="C175" t="n">
         <v>126.620002746582</v>
@@ -5020,7 +5032,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
@@ -5049,7 +5061,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
@@ -5078,11 +5090,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>106.6833877563477</v>
+        <v>106.6834030151367</v>
       </c>
       <c r="C178" t="n">
         <v>116.120002746582</v>
@@ -5107,11 +5119,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>119.3527297973633</v>
+        <v>119.3527145385742</v>
       </c>
       <c r="C179" t="n">
         <v>129.9100036621094</v>
@@ -5136,11 +5148,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>135.8163909912109</v>
+        <v>135.8164367675781</v>
       </c>
       <c r="C180" t="n">
         <v>147.8300018310547</v>
@@ -5165,11 +5177,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>142.1306762695312</v>
+        <v>142.1306610107422</v>
       </c>
       <c r="C181" t="n">
         <v>153.9199981689453</v>
@@ -5194,11 +5206,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>134.5125579833984</v>
+        <v>134.5125427246094</v>
       </c>
       <c r="C182" t="n">
         <v>145.6699981689453</v>
@@ -5223,7 +5235,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
@@ -5252,11 +5264,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>146.5294189453125</v>
+        <v>146.5293884277344</v>
       </c>
       <c r="C184" t="n">
         <v>157.9700012207031</v>
@@ -5281,11 +5293,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>159.1630096435547</v>
+        <v>159.1629943847656</v>
       </c>
       <c r="C185" t="n">
         <v>171.5899963378906</v>
@@ -5310,7 +5322,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
@@ -5339,7 +5351,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
@@ -5368,11 +5380,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>157.2705688476562</v>
+        <v>157.2705383300781</v>
       </c>
       <c r="C188" t="n">
         <v>168.7400054931641</v>
@@ -5397,7 +5409,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
@@ -5426,11 +5438,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>162.3992462158203</v>
+        <v>162.3992309570312</v>
       </c>
       <c r="C190" t="n">
         <v>173.4799957275391</v>
@@ -5455,11 +5467,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>182.9004058837891</v>
+        <v>182.9004364013672</v>
       </c>
       <c r="C191" t="n">
         <v>195.3800048828125</v>
@@ -5484,7 +5496,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
@@ -5513,11 +5525,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>181.7120971679688</v>
+        <v>181.7120819091797</v>
       </c>
       <c r="C193" t="n">
         <v>193.3099975585938</v>
@@ -5542,7 +5554,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
@@ -5571,11 +5583,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>191.4223480224609</v>
+        <v>191.42236328125</v>
       </c>
       <c r="C195" t="n">
         <v>203.6399993896484</v>
@@ -5600,11 +5612,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>201.8321228027344</v>
+        <v>201.8321533203125</v>
       </c>
       <c r="C196" t="n">
         <v>213.8999938964844</v>
@@ -5629,7 +5641,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
@@ -5658,11 +5670,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>199.3693542480469</v>
+        <v>199.369384765625</v>
       </c>
       <c r="C198" t="n">
         <v>211.2899932861328</v>
@@ -5687,11 +5699,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>186.2650909423828</v>
+        <v>186.2650756835938</v>
       </c>
       <c r="C199" t="n">
         <v>196.5800018310547</v>
@@ -5716,11 +5728,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>178.7417297363281</v>
+        <v>178.7417144775391</v>
       </c>
       <c r="C200" t="n">
         <v>188.6399993896484</v>
@@ -5745,11 +5757,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>179.1302185058594</v>
+        <v>179.1302337646484</v>
       </c>
       <c r="C201" t="n">
         <v>189.0500030517578</v>
@@ -5774,11 +5786,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>173.0797576904297</v>
+        <v>173.0797729492188</v>
       </c>
       <c r="C202" t="n">
         <v>181.8800048828125</v>
@@ -5803,11 +5815,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>204.4925842285156</v>
+        <v>204.4925689697266</v>
       </c>
       <c r="C203" t="n">
         <v>214.8899993896484</v>
@@ -5832,11 +5844,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>208.9651947021484</v>
+        <v>208.9651489257812</v>
       </c>
       <c r="C204" t="n">
         <v>219.5899963378906</v>
@@ -5861,7 +5873,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
@@ -5890,7 +5902,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
@@ -5919,11 +5931,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>201.5814666748047</v>
+        <v>201.5814971923828</v>
       </c>
       <c r="C207" t="n">
         <v>211.0200042724609</v>
@@ -5948,7 +5960,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
@@ -5977,7 +5989,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
@@ -6006,11 +6018,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>178.2791442871094</v>
+        <v>178.2791290283203</v>
       </c>
       <c r="C210" t="n">
         <v>185.8000030517578</v>
@@ -6035,7 +6047,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
@@ -6064,7 +6076,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
@@ -6093,7 +6105,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
@@ -6122,11 +6134,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>201.4927673339844</v>
+        <v>201.4927520751953</v>
       </c>
       <c r="C214" t="n">
         <v>208.1799926757812</v>
@@ -6151,11 +6163,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>207.7259063720703</v>
+        <v>207.7258605957031</v>
       </c>
       <c r="C215" t="n">
         <v>214.6199951171875</v>
@@ -6180,7 +6192,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
@@ -6209,11 +6221,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>219.5754852294922</v>
+        <v>219.5754699707031</v>
       </c>
       <c r="C217" t="n">
         <v>226</v>
@@ -6238,11 +6250,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>238.0353851318359</v>
+        <v>238.0353698730469</v>
       </c>
       <c r="C218" t="n">
         <v>245</v>
@@ -6267,11 +6279,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>244.5157928466797</v>
+        <v>244.5157318115234</v>
       </c>
       <c r="C219" t="n">
         <v>251.6699981689453</v>
@@ -6296,7 +6308,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
@@ -6325,11 +6337,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>242.3729400634766</v>
+        <v>242.3729248046875</v>
       </c>
       <c r="C221" t="n">
         <v>248.6399993896484</v>
@@ -6354,11 +6366,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>263.9938659667969</v>
+        <v>263.993896484375</v>
       </c>
       <c r="C222" t="n">
         <v>270.8200073242188</v>
@@ -6383,11 +6395,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>249.5132598876953</v>
+        <v>249.5132751464844</v>
       </c>
       <c r="C223" t="n">
         <v>255.0800018310547</v>
@@ -6412,11 +6424,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>269.6441040039062</v>
+        <v>269.6441345214844</v>
       </c>
       <c r="C224" t="n">
         <v>275.6600036621094</v>
@@ -6441,7 +6453,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
@@ -6470,11 +6482,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>282.98876953125</v>
+        <v>282.9888000488281</v>
       </c>
       <c r="C226" t="n">
         <v>288.3900146484375</v>
@@ -6499,7 +6511,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
@@ -6528,7 +6540,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
@@ -6557,7 +6569,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
@@ -6586,11 +6598,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>267.6725158691406</v>
+        <v>267.6724853515625</v>
       </c>
       <c r="C230" t="n">
         <v>271.8800048828125</v>
@@ -6615,11 +6627,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>281.06201171875</v>
+        <v>281.0620422363281</v>
       </c>
       <c r="C231" t="n">
         <v>285.4800109863281</v>
@@ -6644,11 +6656,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>298.2571105957031</v>
+        <v>298.2571411132812</v>
       </c>
       <c r="C232" t="n">
         <v>301.989990234375</v>
@@ -6673,7 +6685,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -6702,11 +6714,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>293.5263671875</v>
+        <v>293.5263366699219</v>
       </c>
       <c r="C234" t="n">
         <v>297.2000122070312</v>
@@ -6731,7 +6743,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6760,7 +6772,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6789,7 +6801,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6818,7 +6830,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6847,7 +6859,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6876,11 +6888,11 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>293.5030822753906</v>
+        <v>293.5030517578125</v>
       </c>
       <c r="C240" t="n">
         <v>296.1799926757812</v>
@@ -6905,7 +6917,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6934,11 +6946,11 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
-        <v>306.7621459960938</v>
+        <v>306.7621765136719</v>
       </c>
       <c r="C242" t="n">
         <v>309.5599975585938</v>
@@ -6963,7 +6975,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6992,7 +7004,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7021,7 +7033,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7050,11 +7062,11 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
-        <v>309.824462890625</v>
+        <v>309.8244934082031</v>
       </c>
       <c r="C246" t="n">
         <v>311.7300109863281</v>
@@ -7079,7 +7091,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7108,7 +7120,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7137,7 +7149,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7166,32 +7178,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>335.2099914550781</v>
+        <v>334.8399963378906</v>
       </c>
       <c r="C250" t="n">
-        <v>335.2099914550781</v>
+        <v>334.8399963378906</v>
       </c>
       <c r="D250" t="n">
-        <v>26647500</v>
+        <v>27818300</v>
       </c>
       <c r="E250" t="n">
         <v>28.22</v>
       </c>
       <c r="F250" t="n">
-        <v>11.87845469365975</v>
+        <v>11.86534359808259</v>
       </c>
       <c r="G250" t="n">
         <v>387860106</v>
       </c>
       <c r="H250" t="n">
-        <v>130014582818.0257</v>
+        <v>129871076472.6539</v>
       </c>
       <c r="I250" t="n">
-        <v>0.06870389500692808</v>
+        <v>0.07172250914611981</v>
       </c>
     </row>
   </sheetData>
@@ -7223,75 +7235,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40032</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7327,13 +7339,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40126</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7369,13 +7381,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7411,13 +7423,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40032</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7453,13 +7465,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40126</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7495,13 +7507,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7528,7 +7540,7 @@
       <c r="I7" t="n">
         <v>7.54</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K7" t="n">
@@ -7541,13 +7553,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7574,7 +7586,7 @@
       <c r="I8" t="n">
         <v>8.07</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K8" t="n">
@@ -7587,13 +7599,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40396</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7620,7 +7632,7 @@
       <c r="I9" t="n">
         <v>8.470000000000001</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K9" t="n">
@@ -7633,13 +7645,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40490</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7666,7 +7678,7 @@
       <c r="I10" t="n">
         <v>8.98</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K10" t="n">
@@ -7679,13 +7691,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7712,7 +7724,7 @@
       <c r="I11" t="n">
         <v>9.09</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K11" t="n">
@@ -7725,13 +7737,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7758,7 +7770,7 @@
       <c r="I12" t="n">
         <v>7.629999999999999</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="K12" t="n">
@@ -7771,13 +7783,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40759</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7804,7 +7816,7 @@
       <c r="I13" t="n">
         <v>7.42</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40759</v>
       </c>
       <c r="K13" t="n">
@@ -7817,13 +7829,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40850</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7850,7 +7862,7 @@
       <c r="I14" t="n">
         <v>5.36</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40850</v>
       </c>
       <c r="K14" t="n">
@@ -7863,13 +7875,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7896,7 +7908,7 @@
       <c r="I15" t="n">
         <v>4.640000000000001</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="K15" t="n">
@@ -7909,13 +7921,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41031</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7942,7 +7954,7 @@
       <c r="I16" t="n">
         <v>6.720000000000001</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41031</v>
       </c>
       <c r="K16" t="n">
@@ -7955,13 +7967,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41122</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7988,7 +8000,7 @@
       <c r="I17" t="n">
         <v>5.91</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41122</v>
       </c>
       <c r="K17" t="n">
@@ -8001,13 +8013,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8034,7 +8046,7 @@
       <c r="I18" t="n">
         <v>7.859999999999999</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="K18" t="n">
@@ -8047,13 +8059,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8080,7 +8092,7 @@
       <c r="I19" t="n">
         <v>7.880000000000001</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="K19" t="n">
@@ -8093,13 +8105,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41395</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8126,7 +8138,7 @@
       <c r="I20" t="n">
         <v>7.81</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41395</v>
       </c>
       <c r="K20" t="n">
@@ -8139,13 +8151,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8172,7 +8184,7 @@
       <c r="I21" t="n">
         <v>9.44</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="K21" t="n">
@@ -8185,13 +8197,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41577</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8218,7 +8230,7 @@
       <c r="I22" t="n">
         <v>10.24</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41577</v>
       </c>
       <c r="K22" t="n">
@@ -8231,13 +8243,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8264,7 +8276,7 @@
       <c r="I23" t="n">
         <v>10.92</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="K23" t="n">
@@ -8277,13 +8289,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41761</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8310,7 +8322,7 @@
       <c r="I24" t="n">
         <v>10.29</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41761</v>
       </c>
       <c r="K24" t="n">
@@ -8323,13 +8335,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41850</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8356,7 +8368,7 @@
       <c r="I25" t="n">
         <v>9.98</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41850</v>
       </c>
       <c r="K25" t="n">
@@ -8369,13 +8381,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41941</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8402,7 +8414,7 @@
       <c r="I26" t="n">
         <v>9.640000000000001</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41941</v>
       </c>
       <c r="K26" t="n">
@@ -8415,13 +8427,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42062</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8448,7 +8460,7 @@
       <c r="I27" t="n">
         <v>8.4</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42062</v>
       </c>
       <c r="K27" t="n">
@@ -8461,13 +8473,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42123</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8494,7 +8506,7 @@
       <c r="I28" t="n">
         <v>8.309999999999999</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42123</v>
       </c>
       <c r="K28" t="n">
@@ -8507,13 +8519,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42220</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8540,7 +8552,7 @@
       <c r="I29" t="n">
         <v>8.889999999999999</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42220</v>
       </c>
       <c r="K29" t="n">
@@ -8553,13 +8565,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42312</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8586,7 +8598,7 @@
       <c r="I30" t="n">
         <v>8.19</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42312</v>
       </c>
       <c r="K30" t="n">
@@ -8599,13 +8611,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42426</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8632,7 +8644,7 @@
       <c r="I31" t="n">
         <v>8.619999999999999</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42426</v>
       </c>
       <c r="K31" t="n">
@@ -8645,13 +8657,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42500</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8678,7 +8690,7 @@
       <c r="I32" t="n">
         <v>7.539999999999999</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42500</v>
       </c>
       <c r="K32" t="n">
@@ -8691,13 +8703,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42587</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8724,7 +8736,7 @@
       <c r="I33" t="n">
         <v>6.22</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42587</v>
       </c>
       <c r="K33" t="n">
@@ -8737,13 +8749,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8770,7 +8782,7 @@
       <c r="I34" t="n">
         <v>7.48</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="K34" t="n">
@@ -8783,13 +8795,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8816,7 +8828,7 @@
       <c r="I35" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="K35" t="n">
@@ -8829,13 +8841,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42859</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8862,7 +8874,7 @@
       <c r="I36" t="n">
         <v>10.14</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42859</v>
       </c>
       <c r="K36" t="n">
@@ -8875,13 +8887,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42950</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8908,7 +8920,7 @@
       <c r="I37" t="n">
         <v>11.37</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42950</v>
       </c>
       <c r="K37" t="n">
@@ -8921,13 +8933,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43040</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8954,7 +8966,7 @@
       <c r="I38" t="n">
         <v>8.34</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43040</v>
       </c>
       <c r="K38" t="n">
@@ -8967,13 +8979,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43154</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -9000,7 +9012,7 @@
       <c r="I39" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43154</v>
       </c>
       <c r="K39" t="n">
@@ -9013,13 +9025,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43222</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9046,7 +9058,7 @@
       <c r="I40" t="n">
         <v>8.19</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43222</v>
       </c>
       <c r="K40" t="n">
@@ -9059,13 +9071,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43313</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9092,7 +9104,7 @@
       <c r="I41" t="n">
         <v>8.18</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43313</v>
       </c>
       <c r="K41" t="n">
@@ -9105,13 +9117,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43403</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9138,7 +9150,7 @@
       <c r="I42" t="n">
         <v>10.97</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43403</v>
       </c>
       <c r="K42" t="n">
@@ -9151,13 +9163,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9184,7 +9196,7 @@
       <c r="I43" t="n">
         <v>8.459999999999999</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="K43" t="n">
@@ -9197,13 +9209,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43587</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9230,7 +9242,7 @@
       <c r="I44" t="n">
         <v>8.41</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43587</v>
       </c>
       <c r="K44" t="n">
@@ -9243,13 +9255,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9276,7 +9288,7 @@
       <c r="I45" t="n">
         <v>8.15</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="K45" t="n">
@@ -9289,13 +9301,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9322,7 +9334,7 @@
       <c r="I46" t="n">
         <v>7.89</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="K46" t="n">
@@ -9335,13 +9347,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43888</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9368,7 +9380,7 @@
       <c r="I47" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43888</v>
       </c>
       <c r="K47" t="n">
@@ -9381,13 +9393,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43950</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9414,7 +9426,7 @@
       <c r="I48" t="n">
         <v>8</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43950</v>
       </c>
       <c r="K48" t="n">
@@ -9427,13 +9439,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9460,7 +9472,7 @@
       <c r="I49" t="n">
         <v>4.77</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="K49" t="n">
@@ -9473,13 +9485,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9506,7 +9518,7 @@
       <c r="I50" t="n">
         <v>5.02</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="K50" t="n">
@@ -9519,13 +9531,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44252</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9552,7 +9564,7 @@
       <c r="I51" t="n">
         <v>7.789999999999999</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44252</v>
       </c>
       <c r="K51" t="n">
@@ -9565,13 +9577,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9598,7 +9610,7 @@
       <c r="I52" t="n">
         <v>12.31</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="K52" t="n">
@@ -9611,13 +9623,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44406</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9644,7 +9656,7 @@
       <c r="I53" t="n">
         <v>18.1</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44406</v>
       </c>
       <c r="K53" t="n">
@@ -9657,13 +9669,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44497</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9690,7 +9702,7 @@
       <c r="I54" t="n">
         <v>19.65</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44497</v>
       </c>
       <c r="K54" t="n">
@@ -9703,13 +9715,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9736,7 +9748,7 @@
       <c r="I55" t="n">
         <v>19.27</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="K55" t="n">
@@ -9749,13 +9761,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9782,7 +9794,7 @@
       <c r="I56" t="n">
         <v>18.79</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="K56" t="n">
@@ -9795,13 +9807,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44771</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9828,7 +9840,7 @@
       <c r="I57" t="n">
         <v>16.59</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44771</v>
       </c>
       <c r="K57" t="n">
@@ -9841,13 +9853,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44862</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9874,7 +9886,7 @@
       <c r="I58" t="n">
         <v>14.35</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44862</v>
       </c>
       <c r="K58" t="n">
@@ -9887,13 +9899,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44981</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9920,7 +9932,7 @@
       <c r="I59" t="n">
         <v>12.55</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44981</v>
       </c>
       <c r="K59" t="n">
@@ -9933,13 +9945,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45048</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9966,7 +9978,7 @@
       <c r="I60" t="n">
         <v>12.49</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45048</v>
       </c>
       <c r="K60" t="n">
@@ -9979,13 +9991,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45135</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -10012,7 +10024,7 @@
       <c r="I61" t="n">
         <v>13.95</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45135</v>
       </c>
       <c r="K61" t="n">
@@ -10025,13 +10037,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10058,7 +10070,7 @@
       <c r="I62" t="n">
         <v>16.96</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="K62" t="n">
@@ -10071,13 +10083,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45345</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10104,7 +10116,7 @@
       <c r="I63" t="n">
         <v>21.8</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45345</v>
       </c>
       <c r="K63" t="n">
@@ -10117,13 +10129,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45408</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10150,7 +10162,7 @@
       <c r="I64" t="n">
         <v>22.5</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45408</v>
       </c>
       <c r="K64" t="n">
@@ -10163,13 +10175,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45499</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10196,7 +10208,7 @@
       <c r="I65" t="n">
         <v>23.64</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45499</v>
       </c>
       <c r="K65" t="n">
@@ -10209,13 +10221,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45595</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10242,7 +10254,7 @@
       <c r="I66" t="n">
         <v>24.39</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45595</v>
       </c>
       <c r="K66" t="n">
@@ -10255,13 +10267,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45715</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10288,7 +10300,7 @@
       <c r="I67" t="n">
         <v>22.7</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45715</v>
       </c>
       <c r="K67" t="n">
@@ -10301,13 +10313,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45775</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10334,7 +10346,7 @@
       <c r="I68" t="n">
         <v>20.76</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45775</v>
       </c>
       <c r="K68" t="n">
@@ -10347,13 +10359,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45866</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10380,7 +10392,7 @@
       <c r="I69" t="n">
         <v>22.65</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45866</v>
       </c>
       <c r="K69" t="n">
@@ -10393,13 +10405,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45957</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10426,7 +10438,7 @@
       <c r="I70" t="n">
         <v>23.94</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45957</v>
       </c>
       <c r="K70" t="n">
@@ -10439,13 +10451,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46080</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10472,7 +10484,7 @@
       <c r="I71" t="n">
         <v>25.68</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46080</v>
       </c>
       <c r="K71" t="n">
@@ -10485,13 +10497,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46140</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10518,7 +10530,7 @@
       <c r="I72" t="n">
         <v>28.27</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46140</v>
       </c>
       <c r="K72" t="n">
@@ -10531,13 +10543,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46248</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10558,7 +10570,7 @@
       <c r="I73" t="n">
         <v>28.22</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46248</v>
       </c>
       <c r="K73" t="n">
@@ -10595,52 +10607,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40032</v>
       </c>
       <c r="C2" t="n">
@@ -10669,10 +10681,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40126</v>
       </c>
       <c r="C3" t="n">
@@ -10701,10 +10713,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40234</v>
       </c>
       <c r="C4" t="n">
@@ -10733,10 +10745,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40490</v>
       </c>
       <c r="C5" t="n">
@@ -10765,10 +10777,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="C6" t="n">
@@ -10797,10 +10809,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="C7" t="n">
@@ -10829,10 +10841,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40753</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40759</v>
       </c>
       <c r="C8" t="n">
@@ -10861,10 +10873,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40843</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40850</v>
       </c>
       <c r="C9" t="n">
@@ -10893,10 +10905,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40939</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="C10" t="n">
@@ -10925,10 +10937,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>41017</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>41031</v>
       </c>
       <c r="C11" t="n">
@@ -10957,10 +10969,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>41108</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>41122</v>
       </c>
       <c r="C12" t="n">
@@ -10989,10 +11001,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41199</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="C13" t="n">
@@ -11021,10 +11033,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41305</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="C14" t="n">
@@ -11053,10 +11065,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41381</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41395</v>
       </c>
       <c r="C15" t="n">
@@ -11085,10 +11097,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41478</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="C16" t="n">
@@ -11117,10 +11129,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41563</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41577</v>
       </c>
       <c r="C17" t="n">
@@ -11149,10 +11161,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41684</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="C18" t="n">
@@ -11181,10 +11193,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41747</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41761</v>
       </c>
       <c r="C19" t="n">
@@ -11213,10 +11225,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41836</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41850</v>
       </c>
       <c r="C20" t="n">
@@ -11245,10 +11257,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41927</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41941</v>
       </c>
       <c r="C21" t="n">
@@ -11277,10 +11289,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>42048</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>42062</v>
       </c>
       <c r="C22" t="n">
@@ -11309,10 +11321,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42109</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42123</v>
       </c>
       <c r="C23" t="n">
@@ -11341,10 +11353,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42205</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42220</v>
       </c>
       <c r="C24" t="n">
@@ -11373,10 +11385,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42300</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42312</v>
       </c>
       <c r="C25" t="n">
@@ -11405,10 +11417,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42412</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42426</v>
       </c>
       <c r="C26" t="n">
@@ -11437,10 +11449,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42482</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42500</v>
       </c>
       <c r="C27" t="n">
@@ -11469,10 +11481,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42573</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42587</v>
       </c>
       <c r="C28" t="n">
@@ -11501,10 +11513,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42664</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="C29" t="n">
@@ -11533,10 +11545,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42779</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="C30" t="n">
@@ -11565,10 +11577,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42846</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42859</v>
       </c>
       <c r="C31" t="n">
@@ -11597,10 +11609,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42937</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42950</v>
       </c>
       <c r="C32" t="n">
@@ -11629,10 +11641,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>43028</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>43040</v>
       </c>
       <c r="C33" t="n">
@@ -11661,10 +11673,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43143</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43154</v>
       </c>
       <c r="C34" t="n">
@@ -11693,10 +11705,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43209</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43222</v>
       </c>
       <c r="C35" t="n">
@@ -11725,10 +11737,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43301</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43313</v>
       </c>
       <c r="C36" t="n">
@@ -11757,10 +11769,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43391</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43403</v>
       </c>
       <c r="C37" t="n">
@@ -11789,10 +11801,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43510</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="C38" t="n">
@@ -11821,10 +11833,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43573</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43587</v>
       </c>
       <c r="C39" t="n">
@@ -11853,10 +11865,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43663</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="C40" t="n">
@@ -11885,10 +11897,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43755</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="C41" t="n">
@@ -11917,10 +11929,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43874</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43888</v>
       </c>
       <c r="C42" t="n">
@@ -11949,10 +11961,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43938</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43950</v>
       </c>
       <c r="C43" t="n">
@@ -11981,10 +11993,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>44029</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="C44" t="n">
@@ -12013,10 +12025,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44120</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="C45" t="n">
@@ -12045,10 +12057,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44238</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44252</v>
       </c>
       <c r="C46" t="n">
@@ -12077,10 +12089,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44302</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="C47" t="n">
@@ -12109,10 +12121,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44393</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44406</v>
       </c>
       <c r="C48" t="n">
@@ -12141,10 +12153,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44484</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44497</v>
       </c>
       <c r="C49" t="n">
@@ -12173,10 +12185,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44602</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="C50" t="n">
@@ -12205,10 +12217,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44673</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="C51" t="n">
@@ -12237,10 +12249,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44764</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44771</v>
       </c>
       <c r="C52" t="n">
@@ -12269,10 +12281,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44855</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44862</v>
       </c>
       <c r="C53" t="n">
@@ -12301,10 +12313,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44974</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44981</v>
       </c>
       <c r="C54" t="n">
@@ -12333,10 +12345,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>45037</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>45048</v>
       </c>
       <c r="C55" t="n">
@@ -12365,10 +12377,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45128</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45135</v>
       </c>
       <c r="C56" t="n">
@@ -12397,10 +12409,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45210</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="C57" t="n">
@@ -12429,10 +12441,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45338</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45345</v>
       </c>
       <c r="C58" t="n">
@@ -12461,10 +12473,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45401</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45408</v>
       </c>
       <c r="C59" t="n">
@@ -12493,10 +12505,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45492</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45499</v>
       </c>
       <c r="C60" t="n">
@@ -12525,10 +12537,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45588</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45595</v>
       </c>
       <c r="C61" t="n">
@@ -12557,10 +12569,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45708</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45715</v>
       </c>
       <c r="C62" t="n">
@@ -12589,10 +12601,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45765</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45775</v>
       </c>
       <c r="C63" t="n">
@@ -12621,10 +12633,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45859</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45866</v>
       </c>
       <c r="C64" t="n">
@@ -12653,10 +12665,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45951</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45957</v>
       </c>
       <c r="C65" t="n">
@@ -12685,10 +12697,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>46073</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>46080</v>
       </c>
       <c r="C66" t="n">
@@ -12717,10 +12729,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>46133</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>46140</v>
       </c>
       <c r="C67" t="n">
@@ -12767,12 +12779,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/CB.xlsx
+++ b/salidas/empresas/CB.xlsx
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>36.82888412475586</v>
+        <v>36.82891464233398</v>
       </c>
       <c r="C3" t="n">
         <v>55.72999954223633</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>34.52083206176758</v>
+        <v>34.52082443237305</v>
       </c>
       <c r="C4" t="n">
         <v>52.0099983215332</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>34.36152648925781</v>
+        <v>34.36151504516602</v>
       </c>
       <c r="C6" t="n">
         <v>51.77000045776367</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>33.75129699707031</v>
+        <v>33.75130462646484</v>
       </c>
       <c r="C7" t="n">
         <v>50.59000015258789</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>34.37841796875</v>
+        <v>34.37841415405273</v>
       </c>
       <c r="C8" t="n">
         <v>51.52999877929688</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>35.9328727722168</v>
+        <v>35.93288803100586</v>
       </c>
       <c r="C9" t="n">
         <v>53.86000061035156</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>36.67715835571289</v>
+        <v>36.67716979980469</v>
       </c>
       <c r="C10" t="n">
         <v>54.72999954223633</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>38.36593246459961</v>
+        <v>38.36593627929688</v>
       </c>
       <c r="C11" t="n">
         <v>57.25</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>38.09116744995117</v>
+        <v>38.0911750793457</v>
       </c>
       <c r="C12" t="n">
         <v>56.84000015258789</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>40.75833511352539</v>
+        <v>40.75834655761719</v>
       </c>
       <c r="C13" t="n">
         <v>60.56999969482422</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>38.88089752197266</v>
+        <v>38.88091278076172</v>
       </c>
       <c r="C14" t="n">
         <v>57.77999877929688</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>40.18603134155273</v>
+        <v>40.1860237121582</v>
       </c>
       <c r="C17" t="n">
         <v>59.45999908447266</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>42.43849563598633</v>
+        <v>42.43850326538086</v>
       </c>
       <c r="C19" t="n">
         <v>62.52000045776367</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>39.18025970458984</v>
+        <v>39.18024826049805</v>
       </c>
       <c r="C20" t="n">
         <v>57.72000122070312</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>39.20742416381836</v>
+        <v>39.20742034912109</v>
       </c>
       <c r="C21" t="n">
         <v>57.7599983215332</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>41.30469131469727</v>
+        <v>41.30471801757812</v>
       </c>
       <c r="C22" t="n">
         <v>60.56999969482422</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>41.33197402954102</v>
+        <v>41.33199310302734</v>
       </c>
       <c r="C23" t="n">
         <v>60.61000061035156</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>40.80006790161133</v>
+        <v>40.8000602722168</v>
       </c>
       <c r="C24" t="n">
         <v>59.83000183105469</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>42.31157684326172</v>
+        <v>42.31158065795898</v>
       </c>
       <c r="C25" t="n">
         <v>61.77999877929688</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>39.88713073730469</v>
+        <v>39.88711547851562</v>
       </c>
       <c r="C26" t="n">
         <v>58.2400016784668</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>38.51736831665039</v>
+        <v>38.51736450195312</v>
       </c>
       <c r="C27" t="n">
         <v>56.2400016784668</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>37.89439392089844</v>
+        <v>37.89440536499023</v>
       </c>
       <c r="C28" t="n">
         <v>55.06000137329102</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>41.49387741088867</v>
+        <v>41.49388885498047</v>
       </c>
       <c r="C29" t="n">
         <v>60.29000091552734</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>41.34247970581055</v>
+        <v>41.34247589111328</v>
       </c>
       <c r="C30" t="n">
         <v>60.06999969482422</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>38.1074333190918</v>
+        <v>38.10744476318359</v>
       </c>
       <c r="C31" t="n">
         <v>55.09000015258789</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>35.07075119018555</v>
+        <v>35.07075500488281</v>
       </c>
       <c r="C32" t="n">
         <v>50.70000076293945</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>37.44338989257812</v>
+        <v>37.44337844848633</v>
       </c>
       <c r="C34" t="n">
         <v>54.13000106811523</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>39.90570449829102</v>
+        <v>39.90571212768555</v>
       </c>
       <c r="C35" t="n">
         <v>57.36000061035156</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>36.35064697265625</v>
+        <v>36.35064315795898</v>
       </c>
       <c r="C36" t="n">
         <v>52.25</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>36.81678009033203</v>
+        <v>36.81676864624023</v>
       </c>
       <c r="C37" t="n">
         <v>52.91999816894531</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>30.53106307983398</v>
+        <v>30.53107070922852</v>
       </c>
       <c r="C38" t="n">
         <v>43.65999984741211</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>25.53113555908203</v>
+        <v>25.53113746643066</v>
       </c>
       <c r="C39" t="n">
         <v>36.5099983215332</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>28.42902565002441</v>
+        <v>28.42901611328125</v>
       </c>
       <c r="C40" t="n">
         <v>40.40000152587891</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>32.59484100341797</v>
+        <v>32.5948600769043</v>
       </c>
       <c r="C41" t="n">
         <v>46.31999969482422</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>30.95525741577148</v>
+        <v>30.95525932312012</v>
       </c>
       <c r="C42" t="n">
         <v>43.9900016784668</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>31.12414169311523</v>
+        <v>31.1241397857666</v>
       </c>
       <c r="C43" t="n">
         <v>44.22999954223633</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>34.7503776550293</v>
+        <v>34.75037002563477</v>
       </c>
       <c r="C44" t="n">
         <v>49.06000137329102</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>36.96034622192383</v>
+        <v>36.96034240722656</v>
       </c>
       <c r="C45" t="n">
         <v>52.18000030517578</v>
@@ -1340,7 +1340,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>38.08991241455078</v>
+        <v>38.08991622924805</v>
       </c>
       <c r="C46" t="n">
         <v>53.45999908447266</v>
@@ -1365,7 +1365,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>36.59368896484375</v>
+        <v>36.59366607666016</v>
       </c>
       <c r="C47" t="n">
         <v>51.36000061035156</v>
@@ -1390,7 +1390,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>34.7055778503418</v>
+        <v>34.70558166503906</v>
       </c>
       <c r="C48" t="n">
         <v>48.70999908447266</v>
@@ -1415,7 +1415,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>36.13236618041992</v>
+        <v>36.13236236572266</v>
       </c>
       <c r="C49" t="n">
         <v>50.40000152587891</v>
@@ -1440,7 +1440,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>35.3222541809082</v>
+        <v>35.32226943969727</v>
       </c>
       <c r="C50" t="n">
         <v>49.27000045776367</v>
@@ -1465,7 +1465,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>35.83843612670898</v>
+        <v>35.83844375610352</v>
       </c>
       <c r="C51" t="n">
         <v>49.9900016784668</v>
@@ -1490,7 +1490,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>37.71610260009766</v>
+        <v>37.71611404418945</v>
       </c>
       <c r="C52" t="n">
         <v>52.29999923706055</v>
@@ -1515,7 +1515,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>38.3579216003418</v>
+        <v>38.35791778564453</v>
       </c>
       <c r="C53" t="n">
         <v>53.18999862670898</v>
@@ -1540,7 +1540,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>35.45170211791992</v>
+        <v>35.45169448852539</v>
       </c>
       <c r="C54" t="n">
         <v>49.15999984741211</v>
@@ -1565,7 +1565,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>37.12474822998047</v>
+        <v>37.12477493286133</v>
       </c>
       <c r="C55" t="n">
         <v>51.47999954223633</v>
@@ -1590,7 +1590,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>38.51884460449219</v>
+        <v>38.51885604858398</v>
       </c>
       <c r="C56" t="n">
         <v>53.08000183105469</v>
@@ -1615,7 +1615,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>38.80186462402344</v>
+        <v>38.80185317993164</v>
       </c>
       <c r="C57" t="n">
         <v>53.47000122070312</v>
@@ -1640,7 +1640,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>42.51072692871094</v>
+        <v>42.51072311401367</v>
       </c>
       <c r="C58" t="n">
         <v>58.25</v>
@@ -1665,7 +1665,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>43.36457443237305</v>
+        <v>43.36458969116211</v>
       </c>
       <c r="C59" t="n">
         <v>59.41999816894531</v>
@@ -1684,7 +1684,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>42.70774459838867</v>
+        <v>42.7077751159668</v>
       </c>
       <c r="C60" t="n">
         <v>58.52000045776367</v>
@@ -1709,7 +1709,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>45.67722320556641</v>
+        <v>45.67721557617188</v>
       </c>
       <c r="C61" t="n">
         <v>62.25</v>
@@ -1734,7 +1734,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>45.19293212890625</v>
+        <v>45.19293594360352</v>
       </c>
       <c r="C62" t="n">
         <v>61.59000015258789</v>
@@ -1759,7 +1759,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>46.41098785400391</v>
+        <v>46.41099166870117</v>
       </c>
       <c r="C63" t="n">
         <v>63.25</v>
@@ -1788,7 +1788,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>47.72098159790039</v>
+        <v>47.72098541259766</v>
       </c>
       <c r="C64" t="n">
         <v>64.69999694824219</v>
@@ -1817,7 +1817,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>49.60179138183594</v>
+        <v>49.60177230834961</v>
       </c>
       <c r="C65" t="n">
         <v>67.25</v>
@@ -1846,7 +1846,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>50.75978469848633</v>
+        <v>50.75978851318359</v>
       </c>
       <c r="C66" t="n">
         <v>68.81999969482422</v>
@@ -1904,7 +1904,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>49.67121505737305</v>
+        <v>49.67122268676758</v>
       </c>
       <c r="C68" t="n">
         <v>66.98000335693359</v>
@@ -1933,7 +1933,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>47.89143371582031</v>
+        <v>47.89142608642578</v>
       </c>
       <c r="C69" t="n">
         <v>64.58000183105469</v>
@@ -1962,7 +1962,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>45.20026397705078</v>
+        <v>45.20025634765625</v>
       </c>
       <c r="C70" t="n">
         <v>60.59999847412109</v>
@@ -1991,7 +1991,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>53.81514358520508</v>
+        <v>53.81513977050781</v>
       </c>
       <c r="C71" t="n">
         <v>72.15000152587891</v>
@@ -2020,7 +2020,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>51.86094284057617</v>
+        <v>51.8609504699707</v>
       </c>
       <c r="C72" t="n">
         <v>69.52999877929688</v>
@@ -2049,7 +2049,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>52.30101776123047</v>
+        <v>52.30101013183594</v>
       </c>
       <c r="C73" t="n">
         <v>70.12000274658203</v>
@@ -2078,7 +2078,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>52.26233291625977</v>
+        <v>52.26231002807617</v>
       </c>
       <c r="C74" t="n">
         <v>69.59999847412109</v>
@@ -2107,7 +2107,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>53.84671783447266</v>
+        <v>53.84670257568359</v>
       </c>
       <c r="C75" t="n">
         <v>71.70999908447266</v>
@@ -2136,7 +2136,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>55.31958770751953</v>
+        <v>55.31955718994141</v>
       </c>
       <c r="C76" t="n">
         <v>73.19999694824219</v>
@@ -2165,7 +2165,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>57.41295623779297</v>
+        <v>57.4129524230957</v>
       </c>
       <c r="C77" t="n">
         <v>75.97000122070312</v>
@@ -2194,7 +2194,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>54.66209411621094</v>
+        <v>54.6620979309082</v>
       </c>
       <c r="C78" t="n">
         <v>72.33000183105469</v>
@@ -2223,7 +2223,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>56.02241516113281</v>
+        <v>56.02239227294922</v>
       </c>
       <c r="C79" t="n">
         <v>74.12999725341797</v>
@@ -2252,7 +2252,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>55.92564010620117</v>
+        <v>55.92562484741211</v>
       </c>
       <c r="C80" t="n">
         <v>73.5</v>
@@ -2281,7 +2281,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>56.10064697265625</v>
+        <v>56.10062789916992</v>
       </c>
       <c r="C81" t="n">
         <v>73.73000335693359</v>
@@ -2310,7 +2310,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>57.89902496337891</v>
+        <v>57.89903259277344</v>
       </c>
       <c r="C82" t="n">
         <v>75.59999847412109</v>
@@ -2339,7 +2339,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>60.23490524291992</v>
+        <v>60.23492431640625</v>
       </c>
       <c r="C83" t="n">
         <v>78.65000152587891</v>
@@ -2368,7 +2368,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>60.67911529541016</v>
+        <v>60.67911911010742</v>
       </c>
       <c r="C84" t="n">
         <v>79.23000335693359</v>
@@ -2397,7 +2397,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>61.48818969726562</v>
+        <v>61.4881706237793</v>
       </c>
       <c r="C85" t="n">
         <v>79.80000305175781</v>
@@ -2426,7 +2426,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>65.74919128417969</v>
+        <v>65.74917602539062</v>
       </c>
       <c r="C86" t="n">
         <v>85.33000183105469</v>
@@ -2455,7 +2455,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>65.79541778564453</v>
+        <v>65.79541015625</v>
       </c>
       <c r="C87" t="n">
         <v>85.38999938964844</v>
@@ -2484,7 +2484,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>68.93572235107422</v>
+        <v>68.93571472167969</v>
       </c>
       <c r="C88" t="n">
         <v>88.97000122070312</v>
@@ -2513,7 +2513,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>69.06742858886719</v>
+        <v>69.06742095947266</v>
       </c>
       <c r="C89" t="n">
         <v>89.13999938964844</v>
@@ -2542,7 +2542,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>69.48584747314453</v>
+        <v>69.48583984375</v>
       </c>
       <c r="C90" t="n">
         <v>89.68000030517578</v>
@@ -2571,7 +2571,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>69.33085632324219</v>
+        <v>69.33086395263672</v>
       </c>
       <c r="C91" t="n">
         <v>89.48000335693359</v>
@@ -2600,7 +2600,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>71.18412017822266</v>
+        <v>71.18411254882812</v>
       </c>
       <c r="C92" t="n">
         <v>91.37999725341797</v>
@@ -2629,7 +2629,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>68.33303070068359</v>
+        <v>68.33302307128906</v>
       </c>
       <c r="C93" t="n">
         <v>87.72000122070312</v>
@@ -2658,7 +2658,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>73.27457427978516</v>
+        <v>73.27458953857422</v>
       </c>
       <c r="C94" t="n">
         <v>93.55999755859375</v>
@@ -2687,7 +2687,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>74.74698638916016</v>
+        <v>74.74697113037109</v>
       </c>
       <c r="C95" t="n">
         <v>95.44000244140625</v>
@@ -2716,7 +2716,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>80.49553680419922</v>
+        <v>80.49554443359375</v>
       </c>
       <c r="C96" t="n">
         <v>102.7799987792969</v>
@@ -2774,7 +2774,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>73.94251251220703</v>
+        <v>73.94249725341797</v>
       </c>
       <c r="C98" t="n">
         <v>93.80999755859375</v>
@@ -2803,7 +2803,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>77.14265441894531</v>
+        <v>77.14263916015625</v>
       </c>
       <c r="C99" t="n">
         <v>97.87000274658203</v>
@@ -2832,7 +2832,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>78.58003234863281</v>
+        <v>78.58001708984375</v>
       </c>
       <c r="C100" t="n">
         <v>99.05999755859375</v>
@@ -2861,7 +2861,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>81.16603088378906</v>
+        <v>81.16603851318359</v>
       </c>
       <c r="C101" t="n">
         <v>102.3199996948242</v>
@@ -2919,7 +2919,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>82.26074981689453</v>
+        <v>82.26076507568359</v>
       </c>
       <c r="C103" t="n">
         <v>103.6999969482422</v>
@@ -2948,7 +2948,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>79.90401458740234</v>
+        <v>79.90402221679688</v>
       </c>
       <c r="C104" t="n">
         <v>100.0999984741211</v>
@@ -3006,7 +3006,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>84.23062133789062</v>
+        <v>84.2305908203125</v>
       </c>
       <c r="C106" t="n">
         <v>104.870002746582</v>
@@ -3035,7 +3035,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>87.78874206542969</v>
+        <v>87.78875732421875</v>
       </c>
       <c r="C107" t="n">
         <v>109.3000030517578</v>
@@ -3093,7 +3093,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>92.80286407470703</v>
+        <v>92.80284881591797</v>
       </c>
       <c r="C109" t="n">
         <v>114.879997253418</v>
@@ -3122,7 +3122,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>87.21269989013672</v>
+        <v>87.21272277832031</v>
       </c>
       <c r="C110" t="n">
         <v>107.9599990844727</v>
@@ -3151,7 +3151,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>92.10005187988281</v>
+        <v>92.10002899169922</v>
       </c>
       <c r="C111" t="n">
         <v>114.0100021362305</v>
@@ -3180,7 +3180,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>90.59358978271484</v>
+        <v>90.59360504150391</v>
       </c>
       <c r="C112" t="n">
         <v>111.4899978637695</v>
@@ -3209,7 +3209,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>86.93702697753906</v>
+        <v>86.93701171875</v>
       </c>
       <c r="C113" t="n">
         <v>106.9899978637695</v>
@@ -3267,7 +3267,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>83.16455078125</v>
+        <v>83.16458129882812</v>
       </c>
       <c r="C115" t="n">
         <v>101.6800003051758</v>
@@ -3296,7 +3296,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>88.9635009765625</v>
+        <v>88.96348571777344</v>
       </c>
       <c r="C116" t="n">
         <v>108.7699966430664</v>
@@ -3325,7 +3325,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>83.55715942382812</v>
+        <v>83.55713653564453</v>
       </c>
       <c r="C117" t="n">
         <v>102.1600036621094</v>
@@ -3383,7 +3383,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>93.47043609619141</v>
+        <v>93.47045135498047</v>
       </c>
       <c r="C119" t="n">
         <v>113.5400009155273</v>
@@ -3412,7 +3412,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>94.54888153076172</v>
+        <v>94.54889678955078</v>
       </c>
       <c r="C120" t="n">
         <v>114.8499984741211</v>
@@ -3441,7 +3441,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>96.74348449707031</v>
+        <v>96.74346160888672</v>
       </c>
       <c r="C121" t="n">
         <v>116.8499984741211</v>
@@ -3470,7 +3470,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>93.61392211914062</v>
+        <v>93.6138916015625</v>
       </c>
       <c r="C122" t="n">
         <v>113.0699996948242</v>
@@ -3528,7 +3528,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>99.20525360107422</v>
+        <v>99.20520782470703</v>
       </c>
       <c r="C124" t="n">
         <v>119.1500015258789</v>
@@ -3557,7 +3557,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>98.13115692138672</v>
+        <v>98.13114166259766</v>
       </c>
       <c r="C125" t="n">
         <v>117.8600006103516</v>
@@ -3586,7 +3586,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>105.41650390625</v>
+        <v>105.4164657592773</v>
       </c>
       <c r="C126" t="n">
         <v>126.6100006103516</v>
@@ -3615,7 +3615,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>109.450065612793</v>
+        <v>109.4500503540039</v>
       </c>
       <c r="C127" t="n">
         <v>130.7100067138672</v>
@@ -3644,7 +3644,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>104.8865127563477</v>
+        <v>104.8865051269531</v>
       </c>
       <c r="C128" t="n">
         <v>125.2600021362305</v>
@@ -3673,7 +3673,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>106.2848815917969</v>
+        <v>106.2848739624023</v>
       </c>
       <c r="C129" t="n">
         <v>126.9300003051758</v>
@@ -3702,7 +3702,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>105.7957534790039</v>
+        <v>105.795768737793</v>
       </c>
       <c r="C130" t="n">
         <v>125.6500015258789</v>
@@ -3760,7 +3760,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>107.7744216918945</v>
+        <v>107.7744369506836</v>
       </c>
       <c r="C132" t="n">
         <v>128</v>
@@ -3818,7 +3818,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>111.2917404174805</v>
+        <v>111.2917327880859</v>
       </c>
       <c r="C134" t="n">
         <v>131.4900054931641</v>
@@ -3847,7 +3847,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>116.9456405639648</v>
+        <v>116.9456253051758</v>
       </c>
       <c r="C135" t="n">
         <v>138.1699981689453</v>
@@ -3876,7 +3876,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>115.9000396728516</v>
+        <v>115.9000549316406</v>
       </c>
       <c r="C136" t="n">
         <v>136.25</v>
@@ -3905,7 +3905,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>116.7506866455078</v>
+        <v>116.7507019042969</v>
       </c>
       <c r="C137" t="n">
         <v>137.25</v>
@@ -3934,7 +3934,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>121.8034973144531</v>
+        <v>121.8035278320312</v>
       </c>
       <c r="C138" t="n">
         <v>143.1900024414062</v>
@@ -3963,7 +3963,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>124.2758407592773</v>
+        <v>124.2758560180664</v>
       </c>
       <c r="C139" t="n">
         <v>145.3800048828125</v>
@@ -3992,7 +3992,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>125.1990814208984</v>
+        <v>125.199104309082</v>
       </c>
       <c r="C140" t="n">
         <v>146.4600067138672</v>
@@ -4021,7 +4021,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>120.8906936645508</v>
+        <v>120.8907241821289</v>
       </c>
       <c r="C141" t="n">
         <v>141.4199981689453</v>
@@ -4050,7 +4050,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>122.4694290161133</v>
+        <v>122.4693832397461</v>
       </c>
       <c r="C142" t="n">
         <v>142.5500030517578</v>
@@ -4079,7 +4079,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>129.5744476318359</v>
+        <v>129.5744781494141</v>
       </c>
       <c r="C143" t="n">
         <v>150.8200073242188</v>
@@ -4108,7 +4108,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>130.6826782226562</v>
+        <v>130.6826934814453</v>
       </c>
       <c r="C144" t="n">
         <v>152.1100006103516</v>
@@ -4137,7 +4137,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>126.1578521728516</v>
+        <v>126.1579666137695</v>
       </c>
       <c r="C145" t="n">
         <v>146.1300048828125</v>
@@ -4195,7 +4195,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>122.5233001708984</v>
+        <v>122.5233306884766</v>
       </c>
       <c r="C147" t="n">
         <v>141.9199981689453</v>
@@ -4224,7 +4224,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>118.6936340332031</v>
+        <v>118.693603515625</v>
       </c>
       <c r="C148" t="n">
         <v>136.7700042724609</v>
@@ -4253,7 +4253,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>117.7390365600586</v>
+        <v>117.739013671875</v>
       </c>
       <c r="C149" t="n">
         <v>135.6699981689453</v>
@@ -4282,7 +4282,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>113.4172134399414</v>
+        <v>113.4171829223633</v>
       </c>
       <c r="C150" t="n">
         <v>130.6900024414062</v>
@@ -4311,7 +4311,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>110.8710098266602</v>
+        <v>110.8710021972656</v>
       </c>
       <c r="C151" t="n">
         <v>127.0199966430664</v>
@@ -4340,7 +4340,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>121.9563674926758</v>
+        <v>121.9563751220703</v>
       </c>
       <c r="C152" t="n">
         <v>139.7200012207031</v>
@@ -4369,7 +4369,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>118.0459442138672</v>
+        <v>118.0459289550781</v>
       </c>
       <c r="C153" t="n">
         <v>135.2400054931641</v>
@@ -4398,7 +4398,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>117.2602844238281</v>
+        <v>117.26025390625</v>
       </c>
       <c r="C154" t="n">
         <v>133.6399993896484</v>
@@ -4427,7 +4427,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>109.6002655029297</v>
+        <v>109.6002578735352</v>
       </c>
       <c r="C155" t="n">
         <v>124.9100036621094</v>
@@ -4514,7 +4514,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>117.4193649291992</v>
+        <v>117.4193725585938</v>
       </c>
       <c r="C158" t="n">
         <v>133.0500030517578</v>
@@ -4543,7 +4543,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>118.1695022583008</v>
+        <v>118.1695175170898</v>
       </c>
       <c r="C159" t="n">
         <v>133.8999938964844</v>
@@ -4572,7 +4572,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>124.2970352172852</v>
+        <v>124.296989440918</v>
       </c>
       <c r="C160" t="n">
         <v>140.0800018310547</v>
@@ -4601,7 +4601,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>128.8401184082031</v>
+        <v>128.8401489257812</v>
       </c>
       <c r="C161" t="n">
         <v>145.1999969482422</v>
@@ -4630,7 +4630,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>129.6121215820312</v>
+        <v>129.6121063232422</v>
       </c>
       <c r="C162" t="n">
         <v>146.0700073242188</v>
@@ -4659,7 +4659,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>131.3538360595703</v>
+        <v>131.3538665771484</v>
       </c>
       <c r="C163" t="n">
         <v>147.2899932861328</v>
@@ -4717,7 +4717,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>139.3711700439453</v>
+        <v>139.3711547851562</v>
       </c>
       <c r="C165" t="n">
         <v>156.2799987792969</v>
@@ -4746,7 +4746,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>144.6530914306641</v>
+        <v>144.653076171875</v>
       </c>
       <c r="C166" t="n">
         <v>161.4400024414062</v>
@@ -4775,7 +4775,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>136.5710601806641</v>
+        <v>136.5709991455078</v>
       </c>
       <c r="C167" t="n">
         <v>152.4199981689453</v>
@@ -4920,7 +4920,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>101.3254470825195</v>
+        <v>101.3254547119141</v>
       </c>
       <c r="C172" t="n">
         <v>111.6900024414062</v>
@@ -4978,7 +4978,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>110.6242523193359</v>
+        <v>110.6242370605469</v>
       </c>
       <c r="C174" t="n">
         <v>121.9400024414062</v>
@@ -5007,7 +5007,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>115.5649642944336</v>
+        <v>115.5649566650391</v>
       </c>
       <c r="C175" t="n">
         <v>126.620002746582</v>
@@ -5036,7 +5036,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>116.1308288574219</v>
+        <v>116.1308441162109</v>
       </c>
       <c r="C176" t="n">
         <v>127.2399978637695</v>
@@ -5065,7 +5065,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>114.0864105224609</v>
+        <v>114.0863876342773</v>
       </c>
       <c r="C177" t="n">
         <v>125</v>
@@ -5094,7 +5094,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>106.6834030151367</v>
+        <v>106.6833953857422</v>
       </c>
       <c r="C178" t="n">
         <v>116.120002746582</v>
@@ -5123,7 +5123,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>119.3527145385742</v>
+        <v>119.3527374267578</v>
       </c>
       <c r="C179" t="n">
         <v>129.9100036621094</v>
@@ -5152,7 +5152,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>135.8164367675781</v>
+        <v>135.8164672851562</v>
       </c>
       <c r="C180" t="n">
         <v>147.8300018310547</v>
@@ -5210,7 +5210,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>134.5125427246094</v>
+        <v>134.5125885009766</v>
       </c>
       <c r="C182" t="n">
         <v>145.6699981689453</v>
@@ -5239,7 +5239,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>150.1273498535156</v>
+        <v>150.1273193359375</v>
       </c>
       <c r="C183" t="n">
         <v>162.5800018310547</v>
@@ -5268,7 +5268,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>146.5293884277344</v>
+        <v>146.5294036865234</v>
       </c>
       <c r="C184" t="n">
         <v>157.9700012207031</v>
@@ -5297,7 +5297,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>159.1629943847656</v>
+        <v>159.1630096435547</v>
       </c>
       <c r="C185" t="n">
         <v>171.5899963378906</v>
@@ -5326,7 +5326,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>157.6788940429688</v>
+        <v>157.6788635253906</v>
       </c>
       <c r="C186" t="n">
         <v>169.9900054931641</v>
@@ -5355,7 +5355,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>148.1366729736328</v>
+        <v>148.1366577148438</v>
       </c>
       <c r="C187" t="n">
         <v>158.9400024414062</v>
@@ -5442,7 +5442,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>162.3992309570312</v>
+        <v>162.3992156982422</v>
       </c>
       <c r="C190" t="n">
         <v>173.4799957275391</v>
@@ -5471,7 +5471,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>182.9004364013672</v>
+        <v>182.9004516601562</v>
       </c>
       <c r="C191" t="n">
         <v>195.3800048828125</v>
@@ -5529,7 +5529,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>181.7120819091797</v>
+        <v>181.7120971679688</v>
       </c>
       <c r="C193" t="n">
         <v>193.3099975585938</v>
@@ -5558,7 +5558,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>185.4439239501953</v>
+        <v>185.4438934326172</v>
       </c>
       <c r="C194" t="n">
         <v>197.2799987792969</v>
@@ -5587,7 +5587,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>191.42236328125</v>
+        <v>191.4223480224609</v>
       </c>
       <c r="C195" t="n">
         <v>203.6399993896484</v>
@@ -5616,7 +5616,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>201.8321533203125</v>
+        <v>201.8321380615234</v>
       </c>
       <c r="C196" t="n">
         <v>213.8999938964844</v>
@@ -5703,7 +5703,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>186.2650756835938</v>
+        <v>186.2651062011719</v>
       </c>
       <c r="C199" t="n">
         <v>196.5800018310547</v>
@@ -5790,7 +5790,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>173.0797729492188</v>
+        <v>173.0797576904297</v>
       </c>
       <c r="C202" t="n">
         <v>181.8800048828125</v>
@@ -5848,7 +5848,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>208.9651489257812</v>
+        <v>208.9651641845703</v>
       </c>
       <c r="C204" t="n">
         <v>219.5899963378906</v>
@@ -5964,7 +5964,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>186.3199310302734</v>
+        <v>186.3199005126953</v>
       </c>
       <c r="C208" t="n">
         <v>194.1799926757812</v>
@@ -5993,7 +5993,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>193.4011840820312</v>
+        <v>193.4012145996094</v>
       </c>
       <c r="C209" t="n">
         <v>201.5599975585938</v>
@@ -6051,7 +6051,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>185.6107940673828</v>
+        <v>185.6108093261719</v>
       </c>
       <c r="C211" t="n">
         <v>192.5599975585938</v>
@@ -6080,7 +6080,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>197.0331420898438</v>
+        <v>197.0331726074219</v>
       </c>
       <c r="C212" t="n">
         <v>204.4100036621094</v>
@@ -6138,7 +6138,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>201.4927520751953</v>
+        <v>201.4927368164062</v>
       </c>
       <c r="C214" t="n">
         <v>208.1799926757812</v>
@@ -6167,7 +6167,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>207.7258605957031</v>
+        <v>207.7258758544922</v>
       </c>
       <c r="C215" t="n">
         <v>214.6199951171875</v>
@@ -6196,7 +6196,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>222.0601501464844</v>
+        <v>222.0601806640625</v>
       </c>
       <c r="C216" t="n">
         <v>229.4299926757812</v>
@@ -6225,7 +6225,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>219.5754699707031</v>
+        <v>219.5754852294922</v>
       </c>
       <c r="C217" t="n">
         <v>226</v>
@@ -6254,7 +6254,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>238.0353698730469</v>
+        <v>238.0353546142578</v>
       </c>
       <c r="C218" t="n">
         <v>245</v>
@@ -6283,7 +6283,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>244.5157318115234</v>
+        <v>244.5157928466797</v>
       </c>
       <c r="C219" t="n">
         <v>251.6699981689453</v>
@@ -6312,7 +6312,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>252.5985565185547</v>
+        <v>252.5985107421875</v>
       </c>
       <c r="C220" t="n">
         <v>259.1300048828125</v>
@@ -6399,7 +6399,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>249.5132751464844</v>
+        <v>249.5132446289062</v>
       </c>
       <c r="C223" t="n">
         <v>255.0800018310547</v>
@@ -6428,7 +6428,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>269.6441345214844</v>
+        <v>269.6441040039062</v>
       </c>
       <c r="C224" t="n">
         <v>275.6600036621094</v>
@@ -6457,7 +6457,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>277.9782104492188</v>
+        <v>277.9781799316406</v>
       </c>
       <c r="C225" t="n">
         <v>284.1799926757812</v>
@@ -6486,7 +6486,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>282.9888000488281</v>
+        <v>282.9887390136719</v>
       </c>
       <c r="C226" t="n">
         <v>288.3900146484375</v>
@@ -6602,7 +6602,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>267.6724853515625</v>
+        <v>267.6725158691406</v>
       </c>
       <c r="C230" t="n">
         <v>271.8800048828125</v>
@@ -6631,7 +6631,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>281.0620422363281</v>
+        <v>281.06201171875</v>
       </c>
       <c r="C231" t="n">
         <v>285.4800109863281</v>
@@ -6660,7 +6660,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>298.2571411132812</v>
+        <v>298.2571105957031</v>
       </c>
       <c r="C232" t="n">
         <v>301.989990234375</v>
@@ -6718,7 +6718,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>293.5263366699219</v>
+        <v>293.5263671875</v>
       </c>
       <c r="C234" t="n">
         <v>297.2000122070312</v>
